--- a/Atlas/Dog/Czeibert_dictionary.xlsx
+++ b/Atlas/Dog/Czeibert_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\dog_brain_toolkit\Atlas\Dog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9CE031-3A3A-4F3E-A446-2E0D42BB0B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E4D939-DE77-4B03-93A3-D2AFEFD6AF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="labelsDogs" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="339">
   <si>
     <t>Number</t>
   </si>
@@ -1013,6 +1013,42 @@
   </si>
   <si>
     <t>Abbreviation</t>
+  </si>
+  <si>
+    <t>network</t>
+  </si>
+  <si>
+    <t>Dorsal/lateral prefontal</t>
+  </si>
+  <si>
+    <t>Somatomotor</t>
+  </si>
+  <si>
+    <t>Sylvian R</t>
+  </si>
+  <si>
+    <t>Visual</t>
+  </si>
+  <si>
+    <t>Sylvian L</t>
+  </si>
+  <si>
+    <t>Medial prefrontal</t>
+  </si>
+  <si>
+    <t>Anterior cingulate</t>
+  </si>
+  <si>
+    <t>Dorsal posterior cingulate</t>
+  </si>
+  <si>
+    <t>Hippocampal</t>
+  </si>
+  <si>
+    <t>Amygdala</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -1854,15 +1890,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1881,8 +1918,11 @@
       <c r="F1" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1896,7 +1936,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1916,8 +1956,11 @@
         <f>LEFT(E3, SEARCH(".nii.gz", E3) - 1)</f>
         <v>L_gFrontalis</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1937,8 +1980,11 @@
         <f t="shared" ref="F4:F67" si="0">LEFT(E4, SEARCH(".nii.gz", E4) - 1)</f>
         <v>R_gFrontalis</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1958,8 +2004,11 @@
         <f t="shared" si="0"/>
         <v>L_gProreus</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1979,8 +2028,11 @@
         <f t="shared" si="0"/>
         <v>R_gProreus</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2000,8 +2052,11 @@
         <f t="shared" si="0"/>
         <v>L_gCompositusRostralis</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2021,8 +2076,11 @@
         <f t="shared" si="0"/>
         <v>R_gCompositusRostralis</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2042,8 +2100,11 @@
         <f t="shared" si="0"/>
         <v>L_gPrecruciatus</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2063,8 +2124,11 @@
         <f t="shared" si="0"/>
         <v>R_gPrecruciatus</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2084,8 +2148,11 @@
         <f t="shared" si="0"/>
         <v>L_gPostcruciatus</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2105,8 +2172,11 @@
         <f t="shared" si="0"/>
         <v>R_gPostcruciatus</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2126,8 +2196,11 @@
         <f t="shared" si="0"/>
         <v>L_gMarginalis</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2147,8 +2220,11 @@
         <f t="shared" si="0"/>
         <v>R_gMarginalis</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2168,8 +2244,11 @@
         <f t="shared" si="0"/>
         <v>L_gEctomarginalis</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2189,8 +2268,11 @@
         <f t="shared" si="0"/>
         <v>R_gEctomarginalis</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2210,8 +2292,11 @@
         <f t="shared" si="0"/>
         <v>L_gOccipitalis</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2231,8 +2316,11 @@
         <f t="shared" si="0"/>
         <v>R_gOccipitalis</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2252,8 +2340,11 @@
         <f t="shared" si="0"/>
         <v>L_gSuprasylviusRostralis</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2273,8 +2364,11 @@
         <f t="shared" si="0"/>
         <v>R_gSuprasylviusRostralis</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2294,8 +2388,11 @@
         <f t="shared" si="0"/>
         <v>L_gSuprasylviusMedius</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2315,8 +2412,11 @@
         <f t="shared" si="0"/>
         <v>R_gSuprasylviusMedius</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2336,8 +2436,11 @@
         <f t="shared" si="0"/>
         <v>L_gSuprasylviusCaudalis</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2357,8 +2460,11 @@
         <f t="shared" si="0"/>
         <v>R_gSuprasylviusCaudalis</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2378,8 +2484,11 @@
         <f t="shared" si="0"/>
         <v>L_gEctosylviusRostralis</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2399,8 +2508,11 @@
         <f t="shared" si="0"/>
         <v>R_gEctosylviusRostralis</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2420,8 +2532,11 @@
         <f t="shared" si="0"/>
         <v>L_gEctosylviusMedius</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G27" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2441,8 +2556,11 @@
         <f t="shared" si="0"/>
         <v>R_gEctosylviusMedius</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G28" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2462,8 +2580,11 @@
         <f t="shared" si="0"/>
         <v>L_gEctosylviusCaudalis</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2483,8 +2604,11 @@
         <f t="shared" si="0"/>
         <v>R_gEctosylviusCaudalis</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G30" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2504,8 +2628,11 @@
         <f t="shared" si="0"/>
         <v>L_gSylviusRostralis</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G31" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2525,8 +2652,11 @@
         <f t="shared" si="0"/>
         <v>R_gSylviusRostralis</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G32" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2546,8 +2676,11 @@
         <f t="shared" si="0"/>
         <v>L_gSylviusCaudalis</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G33" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2567,8 +2700,11 @@
         <f t="shared" si="0"/>
         <v>R_gSylviusCaudalis</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G34" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2588,8 +2724,11 @@
         <f t="shared" si="0"/>
         <v>L_gCompositusCaudalis</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G35" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2609,8 +2748,11 @@
         <f t="shared" si="0"/>
         <v>R_gCompositusCaudalis</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2630,8 +2772,11 @@
         <f t="shared" si="0"/>
         <v>L_gRectus</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G37" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2651,8 +2796,11 @@
         <f t="shared" si="0"/>
         <v>R_gRectus</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G38" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2672,8 +2820,11 @@
         <f t="shared" si="0"/>
         <v>L_gGenualis</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2693,8 +2844,11 @@
         <f t="shared" si="0"/>
         <v>R_gGenualis</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G40" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2714,8 +2868,11 @@
         <f t="shared" si="0"/>
         <v>L_aSubcallosa</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G41" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2735,8 +2892,11 @@
         <f t="shared" si="0"/>
         <v>R_aSubcallosa</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G42" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2756,8 +2916,11 @@
         <f t="shared" si="0"/>
         <v>L_gCinguli</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G43" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2777,8 +2940,11 @@
         <f t="shared" si="0"/>
         <v>R_gCinguli</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G44" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2798,8 +2964,11 @@
         <f t="shared" si="0"/>
         <v>L_gPresplenialis</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G45" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2819,8 +2988,11 @@
         <f t="shared" si="0"/>
         <v>R_gPresplenialis</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G46" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2840,8 +3012,11 @@
         <f t="shared" si="0"/>
         <v>L_gSplenialis</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G47" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2861,8 +3036,11 @@
         <f t="shared" si="0"/>
         <v>R_gSplenialis</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G48" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2882,8 +3060,11 @@
         <f t="shared" si="0"/>
         <v>L_gParahippocampalis</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G49" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2903,8 +3084,11 @@
         <f t="shared" si="0"/>
         <v>R_gParahippocampalis</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G50" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2924,8 +3108,11 @@
         <f t="shared" si="0"/>
         <v>L_hippocampus</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G51" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2945,8 +3132,11 @@
         <f t="shared" si="0"/>
         <v>R_hippocampus</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G52" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2966,8 +3156,11 @@
         <f t="shared" si="0"/>
         <v>L_lPiriformis</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G53" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2987,8 +3180,11 @@
         <f t="shared" si="0"/>
         <v>R_lPiriformis</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G54" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3009,7 +3205,7 @@
         <v>L_tOlfactorium</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3030,7 +3226,7 @@
         <v>R_tOlfactorium</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3050,8 +3246,11 @@
         <f t="shared" si="0"/>
         <v>L_gDiagonalis</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G57" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3071,8 +3270,11 @@
         <f t="shared" si="0"/>
         <v>R_gDiagonalis</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G58" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3092,8 +3294,11 @@
         <f t="shared" si="0"/>
         <v>L_gParaterminalis</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G59" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3113,8 +3318,11 @@
         <f t="shared" si="0"/>
         <v>R_gParaterminalis</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G60" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3134,8 +3342,11 @@
         <f t="shared" si="0"/>
         <v>L_gOlfactoriusLateralis</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G61" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3155,8 +3366,11 @@
         <f t="shared" si="0"/>
         <v>R_gOlfactoriusLateralis</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G62" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3176,8 +3390,11 @@
         <f t="shared" si="0"/>
         <v>L_Thalamus</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G63" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3197,8 +3414,11 @@
         <f t="shared" si="0"/>
         <v>R_Thalamus</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G64" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3219,7 +3439,7 @@
         <v>L_bOlfactorius</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3240,7 +3460,7 @@
         <v>R_bOlfactorius</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3260,8 +3480,11 @@
         <f t="shared" si="0"/>
         <v>L_nCaudatus</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G67" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3281,8 +3504,11 @@
         <f t="shared" ref="F68:F119" si="1">LEFT(E68, SEARCH(".nii.gz", E68) - 1)</f>
         <v>R_nCaudatus</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G68" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3302,8 +3528,11 @@
         <f t="shared" si="1"/>
         <v>L_InsularCortex</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G69" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3323,8 +3552,11 @@
         <f t="shared" si="1"/>
         <v>R_InsularCortex</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G70" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3345,7 +3577,7 @@
         <v>b_Hypophysis</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3365,8 +3597,11 @@
         <f t="shared" si="1"/>
         <v>b_VermisCerebelli</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G72" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3387,7 +3622,7 @@
         <v>b_Pons</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3408,7 +3643,7 @@
         <v>b_MedullaOblongata</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3429,7 +3664,7 @@
         <v>b_MedullaSpinalis</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3450,7 +3685,7 @@
         <v>b_Mesencephalon</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3471,7 +3706,7 @@
         <v>b_Diencephalon</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3492,7 +3727,7 @@
         <v>b_NervusOpticus</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3512,8 +3747,11 @@
         <f t="shared" si="1"/>
         <v>L_HemispheriumCerebelli</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G79" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3533,8 +3771,11 @@
         <f t="shared" si="1"/>
         <v>R_HemispheriumCerebelli</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G80" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3555,7 +3796,7 @@
         <v>b_CommissuraRostralis</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3576,7 +3817,7 @@
         <v>L_PedunculusOlfactorius</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3597,7 +3838,7 @@
         <v>R_PedunculusOlfactorius</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3617,8 +3858,11 @@
         <f t="shared" si="1"/>
         <v>L_aSeptalis</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G84" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3638,8 +3882,11 @@
         <f t="shared" si="1"/>
         <v>R_aSeptalis</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G85" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3660,7 +3907,7 @@
         <v>L_nEtTractusSpinalisNerviTrigemini</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3681,7 +3928,7 @@
         <v>R_nEtTractusSpinalisNerviTrigemini</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3702,7 +3949,7 @@
         <v>L_nVentralisCaudalisThalamiParsMedialis</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3723,7 +3970,7 @@
         <v>R_nVentralisCaudalisThalamiParsMedialis</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3743,8 +3990,11 @@
         <f t="shared" si="1"/>
         <v>L_Amygdala</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G90" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3764,8 +4014,11 @@
         <f t="shared" si="1"/>
         <v>R_Amygdala</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G91" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3786,7 +4039,7 @@
         <v>b_Encephalon</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E93" t="s">
         <v>298</v>
       </c>
@@ -3795,7 +4048,7 @@
         <v>L_OccipitoTemporal</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E94" t="s">
         <v>299</v>
       </c>
@@ -3804,7 +4057,7 @@
         <v>L_OccipitoTemporalGM</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E95" t="s">
         <v>300</v>
       </c>
@@ -3813,7 +4066,7 @@
         <v>L_gEctosylvius</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E96" t="s">
         <v>301</v>
       </c>
